--- a/Switch Functions/SiC Data tf.xlsx
+++ b/Switch Functions/SiC Data tf.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Component\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Github\Switch Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA72262-FB58-4686-9934-CBBBCA88E774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Switch Functions/SiC Data tf.xlsx
+++ b/Switch Functions/SiC Data tf.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Github\Switch Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Component\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA72262-FB58-4686-9934-CBBBCA88E774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B3697F-219D-45F5-94A3-2554D2D71A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>Part Number</t>
   </si>
@@ -183,12 +183,6 @@
   </si>
   <si>
     <t>Q_gs</t>
-  </si>
-  <si>
-    <t>larger than t_f provided in the datasheet</t>
-  </si>
-  <si>
-    <t>t_f provided in the datasheet sincce not enough data is given to do the calculation</t>
   </si>
 </sst>
 </file>
@@ -300,7 +294,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -347,11 +341,17 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -635,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -1156,7 +1156,7 @@
       <c r="W6" s="2">
         <v>7</v>
       </c>
-      <c r="X6" s="18">
+      <c r="X6" s="16">
         <v>3.8</v>
       </c>
       <c r="Y6" s="2">
@@ -1247,7 +1247,7 @@
       <c r="W7" s="2">
         <v>7</v>
       </c>
-      <c r="X7" s="18">
+      <c r="X7" s="16">
         <v>3.8</v>
       </c>
       <c r="Y7" s="2">
@@ -1338,7 +1338,7 @@
       <c r="W8" s="2">
         <v>7.2</v>
       </c>
-      <c r="X8" s="18">
+      <c r="X8" s="16">
         <v>3.8</v>
       </c>
       <c r="Y8" s="2">
@@ -1538,11 +1538,29 @@
       <c r="A11" s="4"/>
       <c r="B11" s="11"/>
     </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="Q13" s="17"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="18"/>
+    </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="Q14" s="16"/>
-      <c r="R14" s="17" t="s">
-        <v>49</v>
-      </c>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="18"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
@@ -1561,10 +1579,28 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="6"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="17" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="18"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="Q16" s="17"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="18"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q10">

--- a/Switch Functions/SiC Data tf.xlsx
+++ b/Switch Functions/SiC Data tf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Component\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B3697F-219D-45F5-94A3-2554D2D71A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EA49DE-3765-4446-BEB9-6284F4749FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>Part Number</t>
   </si>
@@ -98,9 +98,6 @@
     <t>AIMBG75R016M1HXTMA1</t>
   </si>
   <si>
-    <t>Output Charge [nC]</t>
-  </si>
-  <si>
     <t>E4M0025075J2-TR</t>
   </si>
   <si>
@@ -183,6 +180,12 @@
   </si>
   <si>
     <t>Q_gs</t>
+  </si>
+  <si>
+    <t>Cooling Side</t>
+  </si>
+  <si>
+    <t>Bottom</t>
   </si>
 </sst>
 </file>
@@ -294,7 +297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -344,15 +347,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -635,14 +631,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="11.90625" customWidth="1"/>
     <col min="3" max="3" width="12.90625" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.90625" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="25.36328125" customWidth="1"/>
@@ -660,7 +656,7 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -672,10 +668,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>13</v>
@@ -711,42 +707,42 @@
         <v>10</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="W1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="U1" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z1" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AB1" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>19</v>
@@ -757,8 +753,8 @@
       <c r="D2" s="4">
         <v>0.39</v>
       </c>
-      <c r="E2" s="4">
-        <v>147</v>
+      <c r="E2" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -828,10 +824,10 @@
     </row>
     <row r="3" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4">
         <v>750</v>
@@ -839,8 +835,8 @@
       <c r="D3" s="4">
         <v>0.46</v>
       </c>
-      <c r="E3" s="4">
-        <v>127</v>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -910,7 +906,7 @@
     </row>
     <row r="4" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>11</v>
@@ -921,11 +917,11 @@
       <c r="D4" s="4">
         <v>0.31</v>
       </c>
-      <c r="E4" s="4">
-        <v>350</v>
+      <c r="E4" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4">
         <v>950</v>
@@ -937,10 +933,7 @@
         <f t="shared" ref="I4:I10" si="2">G4+H4</f>
         <v>1075</v>
       </c>
-      <c r="J4" s="4">
-        <f>0.5*(E4*(0.001))*420</f>
-        <v>73.5</v>
-      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="4">
         <v>506</v>
       </c>
@@ -998,7 +991,7 @@
     </row>
     <row r="5" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>12</v>
@@ -1009,8 +1002,8 @@
       <c r="D5" s="4">
         <v>0.54</v>
       </c>
-      <c r="E5" s="4">
-        <v>140</v>
+      <c r="E5" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F5" s="4">
         <v>60</v>
@@ -1085,7 +1078,7 @@
     </row>
     <row r="6" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>17</v>
@@ -1096,7 +1089,9 @@
       <c r="D6" s="4">
         <v>0.37</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F6" s="4">
         <v>58</v>
       </c>
@@ -1176,7 +1171,7 @@
     </row>
     <row r="7" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>18</v>
@@ -1187,9 +1182,11 @@
       <c r="D7" s="4">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="4">
         <v>360</v>
@@ -1267,10 +1264,10 @@
     </row>
     <row r="8" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4">
         <v>750</v>
@@ -1278,9 +1275,11 @@
       <c r="D8" s="4">
         <v>0.54</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2">
         <v>790</v>
@@ -1358,7 +1357,7 @@
     </row>
     <row r="9" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>16</v>
@@ -1369,7 +1368,9 @@
       <c r="D9" s="4">
         <v>0.34</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F9" s="4">
         <v>60</v>
       </c>
@@ -1447,10 +1448,10 @@
     </row>
     <row r="10" spans="1:28" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>750</v>
@@ -1458,9 +1459,11 @@
       <c r="D10" s="4">
         <v>0.53</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="4">
         <v>220</v>
@@ -1538,29 +1541,8 @@
       <c r="A11" s="4"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="Q13" s="17"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="18"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="18"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="18"/>
-    </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="Q14" s="17"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="18"/>
+      <c r="R14" s="17"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
@@ -1579,28 +1561,8 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="6"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="18"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="Q16" s="17"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="18"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="17"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q10">

--- a/Switch Functions/SiC Data tf.xlsx
+++ b/Switch Functions/SiC Data tf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT\Project\GE Vernova\Component\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EA49DE-3765-4446-BEB9-6284F4749FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4BA604-92AF-49F7-95A6-CC641F8CB204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Part Number</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Bottom</t>
+  </si>
+  <si>
+    <t>Pin_Area [mm^2]</t>
   </si>
 </sst>
 </file>
@@ -631,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -652,9 +655,10 @@
     <col min="18" max="24" width="8.7265625" style="2"/>
     <col min="26" max="27" width="8.7265625" style="2"/>
     <col min="28" max="28" width="11" style="2" customWidth="1"/>
+    <col min="29" max="29" width="15.6328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>36</v>
       </c>
@@ -739,8 +743,11 @@
       <c r="AB1" s="13" t="s">
         <v>45</v>
       </c>
+      <c r="AC1" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>32</v>
       </c>
@@ -821,8 +828,12 @@
         <f>(W2+X2)/(2*Y2)</f>
         <v>1.3020833333333335</v>
       </c>
+      <c r="AC2" s="2">
+        <f>9.8*(15-9.05)</f>
+        <v>58.309999999999995</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>34</v>
       </c>
@@ -903,8 +914,12 @@
         <f>(W3+X3)/(2*Y3)</f>
         <v>1.3020833333333335</v>
       </c>
+      <c r="AC3" s="2">
+        <f>9.8*(15-9.05)</f>
+        <v>58.309999999999995</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>27</v>
       </c>
@@ -988,8 +1003,12 @@
         <f t="shared" ref="AB4:AB10" si="4">(W4+X4)/(2*Y4)</f>
         <v>1.15625</v>
       </c>
+      <c r="AC4" s="2">
+        <f>15.85*(18.69-13.79)</f>
+        <v>77.665000000000035</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>28</v>
       </c>
@@ -1075,8 +1094,12 @@
         <f t="shared" si="4"/>
         <v>1.125</v>
       </c>
+      <c r="AC5" s="2">
+        <f>15.85*(18.69-13.79)</f>
+        <v>77.665000000000035</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>30</v>
       </c>
@@ -1169,7 +1192,7 @@
         <v>0.6923076923076924</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>31</v>
       </c>
@@ -1261,8 +1284,12 @@
         <f t="shared" si="4"/>
         <v>0.6923076923076924</v>
       </c>
+      <c r="AC7" s="2">
+        <f>(10.2-0.3)*(15.4-0.3-8.9)</f>
+        <v>61.379999999999981</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -1355,7 +1382,7 @@
         <v>0.70512820512820518</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>29</v>
       </c>
@@ -1445,8 +1472,12 @@
         <f t="shared" si="4"/>
         <v>0.88043478260869568</v>
       </c>
+      <c r="AC9" s="2">
+        <f>9.8*(14.87-9.05)</f>
+        <v>57.035999999999987</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
@@ -1536,15 +1567,19 @@
         <f t="shared" si="4"/>
         <v>0.95555555555555549</v>
       </c>
+      <c r="AC10" s="2">
+        <f>9.8*(14.87-9.05)</f>
+        <v>57.035999999999987</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="11"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="R14" s="17"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="7"/>
       <c r="C15" s="4"/>
